--- a/public/exports-from-60/29189846.xlsx
+++ b/public/exports-from-60/29189846.xlsx
@@ -59,7 +59,7 @@
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Areal (m²)</t>
+          <t xml:space="preserve">Opvarmet BBR-areal (m²)</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
@@ -14164,12 +14164,12 @@
       </c>
       <c r="K189" t="inlineStr">
         <is>
-          <t xml:space="preserve">311279891</t>
+          <t xml:space="preserve">311279903</t>
         </is>
       </c>
       <c r="L189" t="inlineStr">
         <is>
-          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M189" t="inlineStr">
@@ -14314,12 +14314,12 @@
       </c>
       <c r="K191" t="inlineStr">
         <is>
-          <t xml:space="preserve">311279890</t>
+          <t xml:space="preserve">311279903</t>
         </is>
       </c>
       <c r="L191" t="inlineStr">
         <is>
-          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M191" t="inlineStr">
@@ -15214,7 +15214,7 @@
       </c>
       <c r="K203" t="inlineStr">
         <is>
-          <t xml:space="preserve">311282669</t>
+          <t xml:space="preserve">311372348</t>
         </is>
       </c>
       <c r="L203" t="inlineStr">
@@ -32314,7 +32314,7 @@
       </c>
       <c r="K431" t="inlineStr">
         <is>
-          <t xml:space="preserve">311290524</t>
+          <t xml:space="preserve">311373102</t>
         </is>
       </c>
       <c r="L431" t="inlineStr">
@@ -32614,12 +32614,12 @@
       </c>
       <c r="K435" t="inlineStr">
         <is>
-          <t xml:space="preserve">311369509</t>
+          <t xml:space="preserve">311374076</t>
         </is>
       </c>
       <c r="L435" t="inlineStr">
         <is>
-          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M435" t="inlineStr">
@@ -35914,12 +35914,12 @@
       </c>
       <c r="K479" t="inlineStr">
         <is>
-          <t xml:space="preserve">311290661</t>
+          <t xml:space="preserve">311290663</t>
         </is>
       </c>
       <c r="L479" t="inlineStr">
         <is>
-          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M479" t="inlineStr">
@@ -35989,7 +35989,7 @@
       </c>
       <c r="K480" t="inlineStr">
         <is>
-          <t xml:space="preserve">311290666</t>
+          <t xml:space="preserve">311374773</t>
         </is>
       </c>
       <c r="L480" t="inlineStr">
@@ -38989,12 +38989,12 @@
       </c>
       <c r="K520" t="inlineStr">
         <is>
-          <t xml:space="preserve">311291095</t>
+          <t xml:space="preserve">311373742</t>
         </is>
       </c>
       <c r="L520" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
         </is>
       </c>
       <c r="M520" t="inlineStr">
@@ -39664,12 +39664,12 @@
       </c>
       <c r="K529" t="inlineStr">
         <is>
-          <t xml:space="preserve">311293774</t>
+          <t xml:space="preserve">311373757</t>
         </is>
       </c>
       <c r="L529" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
         </is>
       </c>
       <c r="M529" t="inlineStr">
@@ -39889,7 +39889,7 @@
       </c>
       <c r="K532" t="inlineStr">
         <is>
-          <t xml:space="preserve">311293846</t>
+          <t xml:space="preserve">311293847</t>
         </is>
       </c>
       <c r="L532" t="inlineStr">

--- a/public/exports-from-60/29189846.xlsx
+++ b/public/exports-from-60/29189846.xlsx
@@ -17989,7 +17989,7 @@
       </c>
       <c r="K240" t="inlineStr">
         <is>
-          <t xml:space="preserve">311284535</t>
+          <t xml:space="preserve">311368606</t>
         </is>
       </c>
       <c r="L240" t="inlineStr">
@@ -32314,7 +32314,7 @@
       </c>
       <c r="K431" t="inlineStr">
         <is>
-          <t xml:space="preserve">311373102</t>
+          <t xml:space="preserve">311290524</t>
         </is>
       </c>
       <c r="L431" t="inlineStr">

--- a/public/exports-from-60/29189846.xlsx
+++ b/public/exports-from-60/29189846.xlsx
@@ -14164,12 +14164,12 @@
       </c>
       <c r="K189" t="inlineStr">
         <is>
-          <t xml:space="preserve">311279903</t>
+          <t xml:space="preserve">311279891</t>
         </is>
       </c>
       <c r="L189" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
         </is>
       </c>
       <c r="M189" t="inlineStr">
@@ -14314,12 +14314,12 @@
       </c>
       <c r="K191" t="inlineStr">
         <is>
-          <t xml:space="preserve">311279903</t>
+          <t xml:space="preserve">311279890</t>
         </is>
       </c>
       <c r="L191" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
         </is>
       </c>
       <c r="M191" t="inlineStr">
@@ -15214,7 +15214,7 @@
       </c>
       <c r="K203" t="inlineStr">
         <is>
-          <t xml:space="preserve">311372348</t>
+          <t xml:space="preserve">311282669</t>
         </is>
       </c>
       <c r="L203" t="inlineStr">
@@ -17989,7 +17989,7 @@
       </c>
       <c r="K240" t="inlineStr">
         <is>
-          <t xml:space="preserve">311368606</t>
+          <t xml:space="preserve">311284535</t>
         </is>
       </c>
       <c r="L240" t="inlineStr">
@@ -32614,12 +32614,12 @@
       </c>
       <c r="K435" t="inlineStr">
         <is>
-          <t xml:space="preserve">311374076</t>
+          <t xml:space="preserve">311369509</t>
         </is>
       </c>
       <c r="L435" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
         </is>
       </c>
       <c r="M435" t="inlineStr">
@@ -35914,12 +35914,12 @@
       </c>
       <c r="K479" t="inlineStr">
         <is>
-          <t xml:space="preserve">311290663</t>
+          <t xml:space="preserve">311290661</t>
         </is>
       </c>
       <c r="L479" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
         </is>
       </c>
       <c r="M479" t="inlineStr">
@@ -35989,7 +35989,7 @@
       </c>
       <c r="K480" t="inlineStr">
         <is>
-          <t xml:space="preserve">311374773</t>
+          <t xml:space="preserve">311290666</t>
         </is>
       </c>
       <c r="L480" t="inlineStr">
@@ -36791,7 +36791,7 @@
       </c>
       <c r="F491" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stænderpladsen 2</t>
+          <t xml:space="preserve">Tapdrupvej 100</t>
         </is>
       </c>
       <c r="G491" t="inlineStr">
@@ -36801,20 +36801,20 @@
       </c>
       <c r="H491" t="inlineStr">
         <is>
-          <t xml:space="preserve">9431029</t>
+          <t xml:space="preserve">3454867</t>
         </is>
       </c>
       <c r="I491" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J491">
-        <v>1500</v>
+        <v>172</v>
       </c>
       <c r="K491" t="inlineStr">
         <is>
-          <t xml:space="preserve">311368829</t>
+          <t xml:space="preserve">311375099</t>
         </is>
       </c>
       <c r="L491" t="inlineStr">
@@ -36881,15 +36881,15 @@
       </c>
       <c r="I492" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J492">
-        <v>172</v>
+        <v>488</v>
       </c>
       <c r="K492" t="inlineStr">
         <is>
-          <t xml:space="preserve">311375099</t>
+          <t xml:space="preserve">311375102</t>
         </is>
       </c>
       <c r="L492" t="inlineStr">
@@ -36956,15 +36956,15 @@
       </c>
       <c r="I493" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J493">
-        <v>488</v>
+        <v>284</v>
       </c>
       <c r="K493" t="inlineStr">
         <is>
-          <t xml:space="preserve">311375102</t>
+          <t xml:space="preserve">311375108</t>
         </is>
       </c>
       <c r="L493" t="inlineStr">
@@ -37016,7 +37016,7 @@
       </c>
       <c r="F494" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tapdrupvej 100</t>
+          <t xml:space="preserve">Tapdrupvej 100A</t>
         </is>
       </c>
       <c r="G494" t="inlineStr">
@@ -37031,15 +37031,15 @@
       </c>
       <c r="I494" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J494">
-        <v>284</v>
+        <v>273</v>
       </c>
       <c r="K494" t="inlineStr">
         <is>
-          <t xml:space="preserve">311375108</t>
+          <t xml:space="preserve">311368613</t>
         </is>
       </c>
       <c r="L494" t="inlineStr">
@@ -37091,7 +37091,7 @@
       </c>
       <c r="F495" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tapdrupvej 100A</t>
+          <t xml:space="preserve">Tingvej 17</t>
         </is>
       </c>
       <c r="G495" t="inlineStr">
@@ -37101,20 +37101,20 @@
       </c>
       <c r="H495" t="inlineStr">
         <is>
-          <t xml:space="preserve">3454867</t>
+          <t xml:space="preserve">5589413</t>
         </is>
       </c>
       <c r="I495" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">30</t>
         </is>
       </c>
       <c r="J495">
-        <v>273</v>
+        <v>1281</v>
       </c>
       <c r="K495" t="inlineStr">
         <is>
-          <t xml:space="preserve">311368613</t>
+          <t xml:space="preserve">311375539</t>
         </is>
       </c>
       <c r="L495" t="inlineStr">
@@ -37166,7 +37166,7 @@
       </c>
       <c r="F496" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tingvej 17</t>
+          <t xml:space="preserve">Tingvej 5</t>
         </is>
       </c>
       <c r="G496" t="inlineStr">
@@ -37176,20 +37176,20 @@
       </c>
       <c r="H496" t="inlineStr">
         <is>
-          <t xml:space="preserve">5589413</t>
+          <t xml:space="preserve">5591355</t>
         </is>
       </c>
       <c r="I496" t="inlineStr">
         <is>
-          <t xml:space="preserve">30</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="J496">
-        <v>1281</v>
+        <v>3916</v>
       </c>
       <c r="K496" t="inlineStr">
         <is>
-          <t xml:space="preserve">311375539</t>
+          <t xml:space="preserve">311375512</t>
         </is>
       </c>
       <c r="L496" t="inlineStr">
@@ -37241,7 +37241,7 @@
       </c>
       <c r="F497" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tingvej 5</t>
+          <t xml:space="preserve">Vinkelvej 172</t>
         </is>
       </c>
       <c r="G497" t="inlineStr">
@@ -37251,20 +37251,20 @@
       </c>
       <c r="H497" t="inlineStr">
         <is>
-          <t xml:space="preserve">5591355</t>
+          <t xml:space="preserve">4012634</t>
         </is>
       </c>
       <c r="I497" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J497">
-        <v>3916</v>
+        <v>387</v>
       </c>
       <c r="K497" t="inlineStr">
         <is>
-          <t xml:space="preserve">311375512</t>
+          <t xml:space="preserve">311375598</t>
         </is>
       </c>
       <c r="L497" t="inlineStr">
@@ -37316,7 +37316,7 @@
       </c>
       <c r="F498" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vinkelvej 172</t>
+          <t xml:space="preserve">Vinkelvej 18A</t>
         </is>
       </c>
       <c r="G498" t="inlineStr">
@@ -37326,7 +37326,7 @@
       </c>
       <c r="H498" t="inlineStr">
         <is>
-          <t xml:space="preserve">4012634</t>
+          <t xml:space="preserve">8838279</t>
         </is>
       </c>
       <c r="I498" t="inlineStr">
@@ -37335,11 +37335,11 @@
         </is>
       </c>
       <c r="J498">
-        <v>387</v>
+        <v>284</v>
       </c>
       <c r="K498" t="inlineStr">
         <is>
-          <t xml:space="preserve">311375598</t>
+          <t xml:space="preserve">311290692</t>
         </is>
       </c>
       <c r="L498" t="inlineStr">
@@ -37391,17 +37391,17 @@
       </c>
       <c r="F499" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vinkelvej 18A</t>
+          <t xml:space="preserve">Vorningvej 33</t>
         </is>
       </c>
       <c r="G499" t="inlineStr">
         <is>
-          <t xml:space="preserve">8800</t>
+          <t xml:space="preserve">8830</t>
         </is>
       </c>
       <c r="H499" t="inlineStr">
         <is>
-          <t xml:space="preserve">8838279</t>
+          <t xml:space="preserve">3468562</t>
         </is>
       </c>
       <c r="I499" t="inlineStr">
@@ -37410,11 +37410,11 @@
         </is>
       </c>
       <c r="J499">
-        <v>284</v>
+        <v>5165</v>
       </c>
       <c r="K499" t="inlineStr">
         <is>
-          <t xml:space="preserve">311290692</t>
+          <t xml:space="preserve">311375628</t>
         </is>
       </c>
       <c r="L499" t="inlineStr">
@@ -37466,7 +37466,7 @@
       </c>
       <c r="F500" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vorningvej 33</t>
+          <t xml:space="preserve">Vorningvej 33A</t>
         </is>
       </c>
       <c r="G500" t="inlineStr">
@@ -37481,15 +37481,15 @@
       </c>
       <c r="I500" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J500">
-        <v>5165</v>
+        <v>813</v>
       </c>
       <c r="K500" t="inlineStr">
         <is>
-          <t xml:space="preserve">311375628</t>
+          <t xml:space="preserve">311290695</t>
         </is>
       </c>
       <c r="L500" t="inlineStr">
@@ -37541,30 +37541,30 @@
       </c>
       <c r="F501" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vorningvej 33A</t>
+          <t xml:space="preserve">Ådalshøjen 2</t>
         </is>
       </c>
       <c r="G501" t="inlineStr">
         <is>
-          <t xml:space="preserve">8830</t>
+          <t xml:space="preserve">8800</t>
         </is>
       </c>
       <c r="H501" t="inlineStr">
         <is>
-          <t xml:space="preserve">3468562</t>
+          <t xml:space="preserve">8074164</t>
         </is>
       </c>
       <c r="I501" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J501">
-        <v>813</v>
+        <v>722</v>
       </c>
       <c r="K501" t="inlineStr">
         <is>
-          <t xml:space="preserve">311290695</t>
+          <t xml:space="preserve">311375648</t>
         </is>
       </c>
       <c r="L501" t="inlineStr">
@@ -37616,30 +37616,30 @@
       </c>
       <c r="F502" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ådalshøjen 2</t>
+          <t xml:space="preserve">Skolen 1</t>
         </is>
       </c>
       <c r="G502" t="inlineStr">
         <is>
-          <t xml:space="preserve">8800</t>
+          <t xml:space="preserve">7470</t>
         </is>
       </c>
       <c r="H502" t="inlineStr">
         <is>
-          <t xml:space="preserve">8074164</t>
+          <t xml:space="preserve">9214926</t>
         </is>
       </c>
       <c r="I502" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="J502">
-        <v>722</v>
+        <v>225</v>
       </c>
       <c r="K502" t="inlineStr">
         <is>
-          <t xml:space="preserve">311375648</t>
+          <t xml:space="preserve">311372662</t>
         </is>
       </c>
       <c r="L502" t="inlineStr">
@@ -37649,7 +37649,7 @@
       </c>
       <c r="M502" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-12-28</t>
+          <t xml:space="preserve">2027-12-29</t>
         </is>
       </c>
       <c r="N502" t="inlineStr">
@@ -37691,7 +37691,7 @@
       </c>
       <c r="F503" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolen 1</t>
+          <t xml:space="preserve">Skolen 3</t>
         </is>
       </c>
       <c r="G503" t="inlineStr">
@@ -37706,15 +37706,15 @@
       </c>
       <c r="I503" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J503">
-        <v>225</v>
+        <v>2661</v>
       </c>
       <c r="K503" t="inlineStr">
         <is>
-          <t xml:space="preserve">311372662</t>
+          <t xml:space="preserve">311372723</t>
         </is>
       </c>
       <c r="L503" t="inlineStr">
@@ -37781,11 +37781,11 @@
       </c>
       <c r="I504" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="J504">
-        <v>2661</v>
+        <v>190</v>
       </c>
       <c r="K504" t="inlineStr">
         <is>
@@ -37856,11 +37856,11 @@
       </c>
       <c r="I505" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J505">
-        <v>190</v>
+        <v>1945</v>
       </c>
       <c r="K505" t="inlineStr">
         <is>
@@ -37931,11 +37931,11 @@
       </c>
       <c r="I506" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J506">
-        <v>1945</v>
+        <v>422</v>
       </c>
       <c r="K506" t="inlineStr">
         <is>
@@ -38006,11 +38006,11 @@
       </c>
       <c r="I507" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J507">
-        <v>422</v>
+        <v>1025</v>
       </c>
       <c r="K507" t="inlineStr">
         <is>
@@ -38081,11 +38081,11 @@
       </c>
       <c r="I508" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="J508">
-        <v>1025</v>
+        <v>898</v>
       </c>
       <c r="K508" t="inlineStr">
         <is>
@@ -38141,30 +38141,30 @@
       </c>
       <c r="F509" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolen 3</t>
+          <t xml:space="preserve">Egeskovvej 75</t>
         </is>
       </c>
       <c r="G509" t="inlineStr">
         <is>
-          <t xml:space="preserve">7470</t>
+          <t xml:space="preserve">8800</t>
         </is>
       </c>
       <c r="H509" t="inlineStr">
         <is>
-          <t xml:space="preserve">9214926</t>
+          <t xml:space="preserve">3451289</t>
         </is>
       </c>
       <c r="I509" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J509">
-        <v>898</v>
+        <v>1067</v>
       </c>
       <c r="K509" t="inlineStr">
         <is>
-          <t xml:space="preserve">311372723</t>
+          <t xml:space="preserve">311290810</t>
         </is>
       </c>
       <c r="L509" t="inlineStr">
@@ -38174,7 +38174,7 @@
       </c>
       <c r="M509" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-12-29</t>
+          <t xml:space="preserve">2027-12-30</t>
         </is>
       </c>
       <c r="N509" t="inlineStr">
@@ -38231,11 +38231,11 @@
       </c>
       <c r="I510" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">15</t>
         </is>
       </c>
       <c r="J510">
-        <v>1067</v>
+        <v>444</v>
       </c>
       <c r="K510" t="inlineStr">
         <is>
@@ -38306,11 +38306,11 @@
       </c>
       <c r="I511" t="inlineStr">
         <is>
-          <t xml:space="preserve">15</t>
+          <t xml:space="preserve">18</t>
         </is>
       </c>
       <c r="J511">
-        <v>444</v>
+        <v>976</v>
       </c>
       <c r="K511" t="inlineStr">
         <is>
@@ -38381,11 +38381,11 @@
       </c>
       <c r="I512" t="inlineStr">
         <is>
-          <t xml:space="preserve">18</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J512">
-        <v>976</v>
+        <v>1673</v>
       </c>
       <c r="K512" t="inlineStr">
         <is>
@@ -38456,11 +38456,11 @@
       </c>
       <c r="I513" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J513">
-        <v>1673</v>
+        <v>3803</v>
       </c>
       <c r="K513" t="inlineStr">
         <is>
@@ -38531,11 +38531,11 @@
       </c>
       <c r="I514" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="J514">
-        <v>3803</v>
+        <v>380</v>
       </c>
       <c r="K514" t="inlineStr">
         <is>
@@ -38606,15 +38606,15 @@
       </c>
       <c r="I515" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="J515">
-        <v>380</v>
+        <v>306</v>
       </c>
       <c r="K515" t="inlineStr">
         <is>
-          <t xml:space="preserve">311290810</t>
+          <t xml:space="preserve">311290811</t>
         </is>
       </c>
       <c r="L515" t="inlineStr">
@@ -38666,7 +38666,7 @@
       </c>
       <c r="F516" t="inlineStr">
         <is>
-          <t xml:space="preserve">Egeskovvej 75</t>
+          <t xml:space="preserve">Egeskovvej 4</t>
         </is>
       </c>
       <c r="G516" t="inlineStr">
@@ -38676,20 +38676,20 @@
       </c>
       <c r="H516" t="inlineStr">
         <is>
-          <t xml:space="preserve">3451289</t>
+          <t xml:space="preserve">8371196</t>
         </is>
       </c>
       <c r="I516" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">57</t>
         </is>
       </c>
       <c r="J516">
-        <v>306</v>
+        <v>275</v>
       </c>
       <c r="K516" t="inlineStr">
         <is>
-          <t xml:space="preserve">311290811</t>
+          <t xml:space="preserve">311291090</t>
         </is>
       </c>
       <c r="L516" t="inlineStr">
@@ -38699,7 +38699,7 @@
       </c>
       <c r="M516" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-12-30</t>
+          <t xml:space="preserve">2028-01-04</t>
         </is>
       </c>
       <c r="N516" t="inlineStr">
@@ -38741,7 +38741,7 @@
       </c>
       <c r="F517" t="inlineStr">
         <is>
-          <t xml:space="preserve">Egeskovvej 4</t>
+          <t xml:space="preserve">Egeskovvej 4A</t>
         </is>
       </c>
       <c r="G517" t="inlineStr">
@@ -38756,15 +38756,15 @@
       </c>
       <c r="I517" t="inlineStr">
         <is>
-          <t xml:space="preserve">57</t>
+          <t xml:space="preserve">62</t>
         </is>
       </c>
       <c r="J517">
-        <v>275</v>
+        <v>172</v>
       </c>
       <c r="K517" t="inlineStr">
         <is>
-          <t xml:space="preserve">311291090</t>
+          <t xml:space="preserve">311291089</t>
         </is>
       </c>
       <c r="L517" t="inlineStr">
@@ -38816,35 +38816,35 @@
       </c>
       <c r="F518" t="inlineStr">
         <is>
-          <t xml:space="preserve">Egeskovvej 4A</t>
+          <t xml:space="preserve">Gl. Banevej 8</t>
         </is>
       </c>
       <c r="G518" t="inlineStr">
         <is>
-          <t xml:space="preserve">8800</t>
+          <t xml:space="preserve">7470</t>
         </is>
       </c>
       <c r="H518" t="inlineStr">
         <is>
-          <t xml:space="preserve">8371196</t>
+          <t xml:space="preserve">379840, 379841</t>
         </is>
       </c>
       <c r="I518" t="inlineStr">
         <is>
-          <t xml:space="preserve">62</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J518">
-        <v>172</v>
+        <v>3301</v>
       </c>
       <c r="K518" t="inlineStr">
         <is>
-          <t xml:space="preserve">311291089</t>
+          <t xml:space="preserve">311291149</t>
         </is>
       </c>
       <c r="L518" t="inlineStr">
         <is>
-          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M518" t="inlineStr">
@@ -38891,17 +38891,17 @@
       </c>
       <c r="F519" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gl. Banevej 8</t>
+          <t xml:space="preserve">Kærsangervej 252</t>
         </is>
       </c>
       <c r="G519" t="inlineStr">
         <is>
-          <t xml:space="preserve">7470</t>
+          <t xml:space="preserve">8800</t>
         </is>
       </c>
       <c r="H519" t="inlineStr">
         <is>
-          <t xml:space="preserve">379840, 379841</t>
+          <t xml:space="preserve">7715426</t>
         </is>
       </c>
       <c r="I519" t="inlineStr">
@@ -38910,11 +38910,11 @@
         </is>
       </c>
       <c r="J519">
-        <v>3301</v>
+        <v>635</v>
       </c>
       <c r="K519" t="inlineStr">
         <is>
-          <t xml:space="preserve">311291149</t>
+          <t xml:space="preserve">311291095</t>
         </is>
       </c>
       <c r="L519" t="inlineStr">
@@ -38981,20 +38981,20 @@
       </c>
       <c r="I520" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J520">
-        <v>635</v>
+        <v>101</v>
       </c>
       <c r="K520" t="inlineStr">
         <is>
-          <t xml:space="preserve">311373742</t>
+          <t xml:space="preserve">311291095</t>
         </is>
       </c>
       <c r="L520" t="inlineStr">
         <is>
-          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M520" t="inlineStr">
@@ -39041,7 +39041,7 @@
       </c>
       <c r="F521" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kærsangervej 252</t>
+          <t xml:space="preserve">Safranvej 10A</t>
         </is>
       </c>
       <c r="G521" t="inlineStr">
@@ -39051,25 +39051,25 @@
       </c>
       <c r="H521" t="inlineStr">
         <is>
-          <t xml:space="preserve">7715426</t>
+          <t xml:space="preserve">9254134</t>
         </is>
       </c>
       <c r="I521" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J521">
-        <v>101</v>
+        <v>267</v>
       </c>
       <c r="K521" t="inlineStr">
         <is>
-          <t xml:space="preserve">311291095</t>
+          <t xml:space="preserve">311291091</t>
         </is>
       </c>
       <c r="L521" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
         </is>
       </c>
       <c r="M521" t="inlineStr">
@@ -39116,7 +39116,7 @@
       </c>
       <c r="F522" t="inlineStr">
         <is>
-          <t xml:space="preserve">Safranvej 10A</t>
+          <t xml:space="preserve">Safranvej 8A</t>
         </is>
       </c>
       <c r="G522" t="inlineStr">
@@ -39131,15 +39131,15 @@
       </c>
       <c r="I522" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J522">
-        <v>267</v>
+        <v>87</v>
       </c>
       <c r="K522" t="inlineStr">
         <is>
-          <t xml:space="preserve">311291091</t>
+          <t xml:space="preserve">311291092</t>
         </is>
       </c>
       <c r="L522" t="inlineStr">
@@ -39191,7 +39191,7 @@
       </c>
       <c r="F523" t="inlineStr">
         <is>
-          <t xml:space="preserve">Safranvej 8A</t>
+          <t xml:space="preserve">Sct. Laurentii Vej 14C</t>
         </is>
       </c>
       <c r="G523" t="inlineStr">
@@ -39201,25 +39201,25 @@
       </c>
       <c r="H523" t="inlineStr">
         <is>
-          <t xml:space="preserve">9254134</t>
+          <t xml:space="preserve">5591308</t>
         </is>
       </c>
       <c r="I523" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J523">
-        <v>87</v>
+        <v>384</v>
       </c>
       <c r="K523" t="inlineStr">
         <is>
-          <t xml:space="preserve">311291092</t>
+          <t xml:space="preserve">311372532</t>
         </is>
       </c>
       <c r="L523" t="inlineStr">
         <is>
-          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M523" t="inlineStr">
@@ -39266,35 +39266,35 @@
       </c>
       <c r="F524" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sct. Laurentii Vej 14C</t>
+          <t xml:space="preserve">Tjele Møllevej 10</t>
         </is>
       </c>
       <c r="G524" t="inlineStr">
         <is>
-          <t xml:space="preserve">8800</t>
+          <t xml:space="preserve">8830</t>
         </is>
       </c>
       <c r="H524" t="inlineStr">
         <is>
-          <t xml:space="preserve">5591308</t>
+          <t xml:space="preserve">3455227</t>
         </is>
       </c>
       <c r="I524" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J524">
-        <v>384</v>
+        <v>2628</v>
       </c>
       <c r="K524" t="inlineStr">
         <is>
-          <t xml:space="preserve">311372532</t>
+          <t xml:space="preserve">311291101</t>
         </is>
       </c>
       <c r="L524" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
         </is>
       </c>
       <c r="M524" t="inlineStr">
@@ -39341,17 +39341,17 @@
       </c>
       <c r="F525" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tjele Møllevej 10</t>
+          <t xml:space="preserve">Guldblommevej 14</t>
         </is>
       </c>
       <c r="G525" t="inlineStr">
         <is>
-          <t xml:space="preserve">8830</t>
+          <t xml:space="preserve">8800</t>
         </is>
       </c>
       <c r="H525" t="inlineStr">
         <is>
-          <t xml:space="preserve">3455227</t>
+          <t xml:space="preserve">5587531</t>
         </is>
       </c>
       <c r="I525" t="inlineStr">
@@ -39360,11 +39360,11 @@
         </is>
       </c>
       <c r="J525">
-        <v>2628</v>
+        <v>836</v>
       </c>
       <c r="K525" t="inlineStr">
         <is>
-          <t xml:space="preserve">311291101</t>
+          <t xml:space="preserve">311293801</t>
         </is>
       </c>
       <c r="L525" t="inlineStr">
@@ -39374,7 +39374,7 @@
       </c>
       <c r="M525" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-01-04</t>
+          <t xml:space="preserve">2028-01-22</t>
         </is>
       </c>
       <c r="N525" t="inlineStr">
@@ -39416,7 +39416,7 @@
       </c>
       <c r="F526" t="inlineStr">
         <is>
-          <t xml:space="preserve">Guldblommevej 14</t>
+          <t xml:space="preserve">Guldblommevej 16</t>
         </is>
       </c>
       <c r="G526" t="inlineStr">
@@ -39431,7 +39431,7 @@
       </c>
       <c r="I526" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J526">
@@ -39439,7 +39439,7 @@
       </c>
       <c r="K526" t="inlineStr">
         <is>
-          <t xml:space="preserve">311293801</t>
+          <t xml:space="preserve">311293850</t>
         </is>
       </c>
       <c r="L526" t="inlineStr">
@@ -39491,7 +39491,7 @@
       </c>
       <c r="F527" t="inlineStr">
         <is>
-          <t xml:space="preserve">Guldblommevej 16</t>
+          <t xml:space="preserve">Kjeldvej 9</t>
         </is>
       </c>
       <c r="G527" t="inlineStr">
@@ -39501,20 +39501,20 @@
       </c>
       <c r="H527" t="inlineStr">
         <is>
-          <t xml:space="preserve">5587531</t>
+          <t xml:space="preserve">9050255</t>
         </is>
       </c>
       <c r="I527" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J527">
-        <v>836</v>
+        <v>157</v>
       </c>
       <c r="K527" t="inlineStr">
         <is>
-          <t xml:space="preserve">311293850</t>
+          <t xml:space="preserve">311293811</t>
         </is>
       </c>
       <c r="L527" t="inlineStr">
@@ -39566,7 +39566,7 @@
       </c>
       <c r="F528" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kjeldvej 9</t>
+          <t xml:space="preserve">Liseborg Hegn 10A</t>
         </is>
       </c>
       <c r="G528" t="inlineStr">
@@ -39576,7 +39576,7 @@
       </c>
       <c r="H528" t="inlineStr">
         <is>
-          <t xml:space="preserve">9050255</t>
+          <t xml:space="preserve">10227103</t>
         </is>
       </c>
       <c r="I528" t="inlineStr">
@@ -39585,16 +39585,16 @@
         </is>
       </c>
       <c r="J528">
-        <v>157</v>
+        <v>6616</v>
       </c>
       <c r="K528" t="inlineStr">
         <is>
-          <t xml:space="preserve">311293811</t>
+          <t xml:space="preserve">311293774</t>
         </is>
       </c>
       <c r="L528" t="inlineStr">
         <is>
-          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M528" t="inlineStr">
@@ -39641,7 +39641,7 @@
       </c>
       <c r="F529" t="inlineStr">
         <is>
-          <t xml:space="preserve">Liseborg Hegn 10A</t>
+          <t xml:space="preserve">Ll. Sct. Hans Gade 7</t>
         </is>
       </c>
       <c r="G529" t="inlineStr">
@@ -39651,20 +39651,20 @@
       </c>
       <c r="H529" t="inlineStr">
         <is>
-          <t xml:space="preserve">10227103</t>
+          <t xml:space="preserve">100002554</t>
         </is>
       </c>
       <c r="I529" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J529">
-        <v>6616</v>
+        <v>464</v>
       </c>
       <c r="K529" t="inlineStr">
         <is>
-          <t xml:space="preserve">311373757</t>
+          <t xml:space="preserve">311373762</t>
         </is>
       </c>
       <c r="L529" t="inlineStr">
@@ -39716,7 +39716,7 @@
       </c>
       <c r="F530" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ll. Sct. Hans Gade 7</t>
+          <t xml:space="preserve">Ll. Sct. Hans Gade 9</t>
         </is>
       </c>
       <c r="G530" t="inlineStr">
@@ -39731,11 +39731,11 @@
       </c>
       <c r="I530" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J530">
-        <v>464</v>
+        <v>1037</v>
       </c>
       <c r="K530" t="inlineStr">
         <is>
@@ -39791,7 +39791,7 @@
       </c>
       <c r="F531" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ll. Sct. Hans Gade 9</t>
+          <t xml:space="preserve">Merkurvej 71</t>
         </is>
       </c>
       <c r="G531" t="inlineStr">
@@ -39801,7 +39801,7 @@
       </c>
       <c r="H531" t="inlineStr">
         <is>
-          <t xml:space="preserve">100002554</t>
+          <t xml:space="preserve">3449917</t>
         </is>
       </c>
       <c r="I531" t="inlineStr">
@@ -39810,11 +39810,11 @@
         </is>
       </c>
       <c r="J531">
-        <v>1037</v>
+        <v>594</v>
       </c>
       <c r="K531" t="inlineStr">
         <is>
-          <t xml:space="preserve">311373762</t>
+          <t xml:space="preserve">311293846</t>
         </is>
       </c>
       <c r="L531" t="inlineStr">
@@ -39866,7 +39866,7 @@
       </c>
       <c r="F532" t="inlineStr">
         <is>
-          <t xml:space="preserve">Merkurvej 71</t>
+          <t xml:space="preserve">Rødevej 2A</t>
         </is>
       </c>
       <c r="G532" t="inlineStr">
@@ -39876,7 +39876,7 @@
       </c>
       <c r="H532" t="inlineStr">
         <is>
-          <t xml:space="preserve">3449917</t>
+          <t xml:space="preserve">8940099</t>
         </is>
       </c>
       <c r="I532" t="inlineStr">
@@ -39885,11 +39885,11 @@
         </is>
       </c>
       <c r="J532">
-        <v>594</v>
+        <v>1569</v>
       </c>
       <c r="K532" t="inlineStr">
         <is>
-          <t xml:space="preserve">311293847</t>
+          <t xml:space="preserve">311374142</t>
         </is>
       </c>
       <c r="L532" t="inlineStr">
@@ -39941,7 +39941,7 @@
       </c>
       <c r="F533" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rødevej 2A</t>
+          <t xml:space="preserve">Rødevej 2D</t>
         </is>
       </c>
       <c r="G533" t="inlineStr">
@@ -39956,15 +39956,15 @@
       </c>
       <c r="I533" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J533">
-        <v>1569</v>
+        <v>150</v>
       </c>
       <c r="K533" t="inlineStr">
         <is>
-          <t xml:space="preserve">311374142</t>
+          <t xml:space="preserve">311374136</t>
         </is>
       </c>
       <c r="L533" t="inlineStr">
@@ -40016,30 +40016,30 @@
       </c>
       <c r="F534" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rødevej 2D</t>
+          <t xml:space="preserve">Skolegade 27</t>
         </is>
       </c>
       <c r="G534" t="inlineStr">
         <is>
-          <t xml:space="preserve">8800</t>
+          <t xml:space="preserve">9632</t>
         </is>
       </c>
       <c r="H534" t="inlineStr">
         <is>
-          <t xml:space="preserve">8940099</t>
+          <t xml:space="preserve">3464052</t>
         </is>
       </c>
       <c r="I534" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J534">
-        <v>150</v>
+        <v>2918</v>
       </c>
       <c r="K534" t="inlineStr">
         <is>
-          <t xml:space="preserve">311374136</t>
+          <t xml:space="preserve">311372613</t>
         </is>
       </c>
       <c r="L534" t="inlineStr">
@@ -40106,15 +40106,15 @@
       </c>
       <c r="I535" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">11</t>
         </is>
       </c>
       <c r="J535">
-        <v>2918</v>
+        <v>156</v>
       </c>
       <c r="K535" t="inlineStr">
         <is>
-          <t xml:space="preserve">311372613</t>
+          <t xml:space="preserve">311374194</t>
         </is>
       </c>
       <c r="L535" t="inlineStr">
@@ -40181,15 +40181,15 @@
       </c>
       <c r="I536" t="inlineStr">
         <is>
-          <t xml:space="preserve">11</t>
+          <t xml:space="preserve">12</t>
         </is>
       </c>
       <c r="J536">
-        <v>156</v>
+        <v>294</v>
       </c>
       <c r="K536" t="inlineStr">
         <is>
-          <t xml:space="preserve">311374194</t>
+          <t xml:space="preserve">311374196</t>
         </is>
       </c>
       <c r="L536" t="inlineStr">
@@ -40256,15 +40256,15 @@
       </c>
       <c r="I537" t="inlineStr">
         <is>
-          <t xml:space="preserve">12</t>
+          <t xml:space="preserve">13</t>
         </is>
       </c>
       <c r="J537">
-        <v>294</v>
+        <v>178</v>
       </c>
       <c r="K537" t="inlineStr">
         <is>
-          <t xml:space="preserve">311374196</t>
+          <t xml:space="preserve">311293836</t>
         </is>
       </c>
       <c r="L537" t="inlineStr">
@@ -40331,15 +40331,15 @@
       </c>
       <c r="I538" t="inlineStr">
         <is>
-          <t xml:space="preserve">13</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J538">
-        <v>178</v>
+        <v>2275</v>
       </c>
       <c r="K538" t="inlineStr">
         <is>
-          <t xml:space="preserve">311293836</t>
+          <t xml:space="preserve">311293831</t>
         </is>
       </c>
       <c r="L538" t="inlineStr">
@@ -40406,15 +40406,15 @@
       </c>
       <c r="I539" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J539">
-        <v>2275</v>
+        <v>333</v>
       </c>
       <c r="K539" t="inlineStr">
         <is>
-          <t xml:space="preserve">311293831</t>
+          <t xml:space="preserve">311293833</t>
         </is>
       </c>
       <c r="L539" t="inlineStr">
@@ -40466,7 +40466,7 @@
       </c>
       <c r="F540" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolegade 27</t>
+          <t xml:space="preserve">Skolegade 29</t>
         </is>
       </c>
       <c r="G540" t="inlineStr">
@@ -40481,15 +40481,15 @@
       </c>
       <c r="I540" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J540">
-        <v>333</v>
+        <v>297</v>
       </c>
       <c r="K540" t="inlineStr">
         <is>
-          <t xml:space="preserve">311293833</t>
+          <t xml:space="preserve">311374191</t>
         </is>
       </c>
       <c r="L540" t="inlineStr">
@@ -40541,40 +40541,40 @@
       </c>
       <c r="F541" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolegade 29</t>
+          <t xml:space="preserve">Liseborgvej 35A</t>
         </is>
       </c>
       <c r="G541" t="inlineStr">
         <is>
-          <t xml:space="preserve">9632</t>
+          <t xml:space="preserve">8800</t>
         </is>
       </c>
       <c r="H541" t="inlineStr">
         <is>
-          <t xml:space="preserve">3464052</t>
+          <t xml:space="preserve">1508276, 100535682</t>
         </is>
       </c>
       <c r="I541" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">12</t>
         </is>
       </c>
       <c r="J541">
-        <v>297</v>
+        <v>854</v>
       </c>
       <c r="K541" t="inlineStr">
         <is>
-          <t xml:space="preserve">311374191</t>
+          <t xml:space="preserve">311373759</t>
         </is>
       </c>
       <c r="L541" t="inlineStr">
         <is>
-          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M541" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-01-22</t>
+          <t xml:space="preserve">2028-02-15</t>
         </is>
       </c>
       <c r="N541" t="inlineStr">
@@ -40616,40 +40616,40 @@
       </c>
       <c r="F542" t="inlineStr">
         <is>
-          <t xml:space="preserve">Liseborgvej 35A</t>
+          <t xml:space="preserve">Brandstrupvej 27</t>
         </is>
       </c>
       <c r="G542" t="inlineStr">
         <is>
-          <t xml:space="preserve">8800</t>
+          <t xml:space="preserve">8840</t>
         </is>
       </c>
       <c r="H542" t="inlineStr">
         <is>
-          <t xml:space="preserve">1508276, 100535682</t>
+          <t xml:space="preserve">4011561</t>
         </is>
       </c>
       <c r="I542" t="inlineStr">
         <is>
-          <t xml:space="preserve">12</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J542">
-        <v>854</v>
+        <v>1178</v>
       </c>
       <c r="K542" t="inlineStr">
         <is>
-          <t xml:space="preserve">311373759</t>
+          <t xml:space="preserve">311369993</t>
         </is>
       </c>
       <c r="L542" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Dansk Energisyn</t>
         </is>
       </c>
       <c r="M542" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-02-15</t>
+          <t xml:space="preserve">2029-04-09</t>
         </is>
       </c>
       <c r="N542" t="inlineStr">
@@ -40691,40 +40691,40 @@
       </c>
       <c r="F543" t="inlineStr">
         <is>
-          <t xml:space="preserve">Brandstrupvej 27</t>
+          <t xml:space="preserve">Guldbækvej 11</t>
         </is>
       </c>
       <c r="G543" t="inlineStr">
         <is>
-          <t xml:space="preserve">8840</t>
+          <t xml:space="preserve">8800</t>
         </is>
       </c>
       <c r="H543" t="inlineStr">
         <is>
-          <t xml:space="preserve">4011561</t>
+          <t xml:space="preserve">5593617</t>
         </is>
       </c>
       <c r="I543" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J543">
-        <v>1178</v>
+        <v>177</v>
       </c>
       <c r="K543" t="inlineStr">
         <is>
-          <t xml:space="preserve">311369993</t>
+          <t xml:space="preserve">311445381</t>
         </is>
       </c>
       <c r="L543" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dansk Energisyn</t>
+          <t xml:space="preserve">Botjek A/S</t>
         </is>
       </c>
       <c r="M543" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-04-09</t>
+          <t xml:space="preserve">2030-06-23</t>
         </is>
       </c>
       <c r="N543" t="inlineStr">
@@ -40766,40 +40766,40 @@
       </c>
       <c r="F544" t="inlineStr">
         <is>
-          <t xml:space="preserve">Guldbækvej 11</t>
+          <t xml:space="preserve">Stadionvej 6A</t>
         </is>
       </c>
       <c r="G544" t="inlineStr">
         <is>
-          <t xml:space="preserve">8800</t>
+          <t xml:space="preserve">8832</t>
         </is>
       </c>
       <c r="H544" t="inlineStr">
         <is>
-          <t xml:space="preserve">5593617</t>
+          <t xml:space="preserve">3464853</t>
         </is>
       </c>
       <c r="I544" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J544">
-        <v>177</v>
+        <v>335</v>
       </c>
       <c r="K544" t="inlineStr">
         <is>
-          <t xml:space="preserve">311445381</t>
+          <t xml:space="preserve">311467972</t>
         </is>
       </c>
       <c r="L544" t="inlineStr">
         <is>
-          <t xml:space="preserve">Botjek A/S</t>
+          <t xml:space="preserve">Dansk Bygningsrådgivning ApS</t>
         </is>
       </c>
       <c r="M544" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-06-23</t>
+          <t xml:space="preserve">2030-10-19</t>
         </is>
       </c>
       <c r="N544" t="inlineStr">
@@ -40841,40 +40841,40 @@
       </c>
       <c r="F545" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stadionvej 6A</t>
+          <t xml:space="preserve">Rørsangervej 5</t>
         </is>
       </c>
       <c r="G545" t="inlineStr">
         <is>
-          <t xml:space="preserve">8832</t>
+          <t xml:space="preserve">8800</t>
         </is>
       </c>
       <c r="H545" t="inlineStr">
         <is>
-          <t xml:space="preserve">3464853</t>
+          <t xml:space="preserve">5586340</t>
         </is>
       </c>
       <c r="I545" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">13</t>
         </is>
       </c>
       <c r="J545">
-        <v>335</v>
+        <v>313</v>
       </c>
       <c r="K545" t="inlineStr">
         <is>
-          <t xml:space="preserve">311467972</t>
+          <t xml:space="preserve">311476458</t>
         </is>
       </c>
       <c r="L545" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dansk Bygningsrådgivning ApS</t>
+          <t xml:space="preserve">Ydes Bygningsrådgivning</t>
         </is>
       </c>
       <c r="M545" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-10-19</t>
+          <t xml:space="preserve">2030-11-17</t>
         </is>
       </c>
       <c r="N545" t="inlineStr">
@@ -40916,7 +40916,7 @@
       </c>
       <c r="F546" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rørsangervej 5</t>
+          <t xml:space="preserve">Søakset 2</t>
         </is>
       </c>
       <c r="G546" t="inlineStr">
@@ -40926,30 +40926,30 @@
       </c>
       <c r="H546" t="inlineStr">
         <is>
-          <t xml:space="preserve">5586340</t>
+          <t xml:space="preserve">100124844</t>
         </is>
       </c>
       <c r="I546" t="inlineStr">
         <is>
-          <t xml:space="preserve">13</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J546">
-        <v>313</v>
+        <v>1565</v>
       </c>
       <c r="K546" t="inlineStr">
         <is>
-          <t xml:space="preserve">311476458</t>
+          <t xml:space="preserve">311505527</t>
         </is>
       </c>
       <c r="L546" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ydes Bygningsrådgivning</t>
+          <t xml:space="preserve">Trykprøvning &amp; Energimærkning Danmark ApS</t>
         </is>
       </c>
       <c r="M546" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-11-17</t>
+          <t xml:space="preserve">2031-03-22</t>
         </is>
       </c>
       <c r="N546" t="inlineStr">
@@ -40991,40 +40991,40 @@
       </c>
       <c r="F547" t="inlineStr">
         <is>
-          <t xml:space="preserve">Søakset 2</t>
+          <t xml:space="preserve">Naundrupvej 7A</t>
         </is>
       </c>
       <c r="G547" t="inlineStr">
         <is>
-          <t xml:space="preserve">8800</t>
+          <t xml:space="preserve">9632</t>
         </is>
       </c>
       <c r="H547" t="inlineStr">
         <is>
-          <t xml:space="preserve">100124844</t>
+          <t xml:space="preserve">749066, 3456742</t>
         </is>
       </c>
       <c r="I547" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J547">
-        <v>1565</v>
+        <v>348</v>
       </c>
       <c r="K547" t="inlineStr">
         <is>
-          <t xml:space="preserve">311505527</t>
+          <t xml:space="preserve">311540479</t>
         </is>
       </c>
       <c r="L547" t="inlineStr">
         <is>
-          <t xml:space="preserve">Trykprøvning &amp; Energimærkning Danmark ApS</t>
+          <t xml:space="preserve">Energi- og Bygningsrådgivning A/S</t>
         </is>
       </c>
       <c r="M547" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-03-22</t>
+          <t xml:space="preserve">2031-08-12</t>
         </is>
       </c>
       <c r="N547" t="inlineStr">
@@ -41066,40 +41066,40 @@
       </c>
       <c r="F548" t="inlineStr">
         <is>
-          <t xml:space="preserve">Naundrupvej 7A</t>
+          <t xml:space="preserve">Anlægsgade 2</t>
         </is>
       </c>
       <c r="G548" t="inlineStr">
         <is>
-          <t xml:space="preserve">9632</t>
+          <t xml:space="preserve">7850</t>
         </is>
       </c>
       <c r="H548" t="inlineStr">
         <is>
-          <t xml:space="preserve">749066, 3456742</t>
+          <t xml:space="preserve">384187, 384188</t>
         </is>
       </c>
       <c r="I548" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J548">
-        <v>348</v>
+        <v>3245</v>
       </c>
       <c r="K548" t="inlineStr">
         <is>
-          <t xml:space="preserve">311540479</t>
+          <t xml:space="preserve">311619862</t>
         </is>
       </c>
       <c r="L548" t="inlineStr">
         <is>
-          <t xml:space="preserve">Energi- og Bygningsrådgivning A/S</t>
+          <t xml:space="preserve">Sweco Danmark A/S - LBF</t>
         </is>
       </c>
       <c r="M548" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-08-12</t>
+          <t xml:space="preserve">2032-08-11</t>
         </is>
       </c>
       <c r="N548" t="inlineStr">
@@ -41141,17 +41141,17 @@
       </c>
       <c r="F549" t="inlineStr">
         <is>
-          <t xml:space="preserve">Anlægsgade 2</t>
+          <t xml:space="preserve">Tingvej 20</t>
         </is>
       </c>
       <c r="G549" t="inlineStr">
         <is>
-          <t xml:space="preserve">7850</t>
+          <t xml:space="preserve">8800</t>
         </is>
       </c>
       <c r="H549" t="inlineStr">
         <is>
-          <t xml:space="preserve">384187, 384188</t>
+          <t xml:space="preserve">5589417</t>
         </is>
       </c>
       <c r="I549" t="inlineStr">
@@ -41160,21 +41160,21 @@
         </is>
       </c>
       <c r="J549">
-        <v>3245</v>
+        <v>8141</v>
       </c>
       <c r="K549" t="inlineStr">
         <is>
-          <t xml:space="preserve">311619862</t>
+          <t xml:space="preserve">311652390</t>
         </is>
       </c>
       <c r="L549" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sweco Danmark A/S - LBF</t>
+          <t xml:space="preserve">Norconsult A/S</t>
         </is>
       </c>
       <c r="M549" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-08-11</t>
+          <t xml:space="preserve">2033-01-04</t>
         </is>
       </c>
       <c r="N549" t="inlineStr">
@@ -41216,7 +41216,7 @@
       </c>
       <c r="F550" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tingvej 20</t>
+          <t xml:space="preserve">H.C. Andersens Vej 5</t>
         </is>
       </c>
       <c r="G550" t="inlineStr">
@@ -41226,30 +41226,30 @@
       </c>
       <c r="H550" t="inlineStr">
         <is>
-          <t xml:space="preserve">5589417</t>
+          <t xml:space="preserve">5590613</t>
         </is>
       </c>
       <c r="I550" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">15</t>
         </is>
       </c>
       <c r="J550">
-        <v>8141</v>
+        <v>478</v>
       </c>
       <c r="K550" t="inlineStr">
         <is>
-          <t xml:space="preserve">311652390</t>
+          <t xml:space="preserve">311659256</t>
         </is>
       </c>
       <c r="L550" t="inlineStr">
         <is>
-          <t xml:space="preserve">Norconsult A/S</t>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
         </is>
       </c>
       <c r="M550" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-01-04</t>
+          <t xml:space="preserve">2033-02-09</t>
         </is>
       </c>
       <c r="N550" t="inlineStr">
@@ -41291,7 +41291,7 @@
       </c>
       <c r="F551" t="inlineStr">
         <is>
-          <t xml:space="preserve">H.C. Andersens Vej 5</t>
+          <t xml:space="preserve">Rørsangervej 5</t>
         </is>
       </c>
       <c r="G551" t="inlineStr">
@@ -41301,30 +41301,30 @@
       </c>
       <c r="H551" t="inlineStr">
         <is>
-          <t xml:space="preserve">5590613</t>
+          <t xml:space="preserve">5586340</t>
         </is>
       </c>
       <c r="I551" t="inlineStr">
         <is>
-          <t xml:space="preserve">15</t>
+          <t xml:space="preserve">14</t>
         </is>
       </c>
       <c r="J551">
-        <v>478</v>
+        <v>357</v>
       </c>
       <c r="K551" t="inlineStr">
         <is>
-          <t xml:space="preserve">311659256</t>
+          <t xml:space="preserve">311661783</t>
         </is>
       </c>
       <c r="L551" t="inlineStr">
         <is>
-          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+          <t xml:space="preserve">Tæthedskompagniet ApS</t>
         </is>
       </c>
       <c r="M551" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-02-09</t>
+          <t xml:space="preserve">2033-02-22</t>
         </is>
       </c>
       <c r="N551" t="inlineStr">
@@ -41366,40 +41366,40 @@
       </c>
       <c r="F552" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rørsangervej 5</t>
+          <t xml:space="preserve">Stadionvej 18</t>
         </is>
       </c>
       <c r="G552" t="inlineStr">
         <is>
-          <t xml:space="preserve">8800</t>
+          <t xml:space="preserve">7850</t>
         </is>
       </c>
       <c r="H552" t="inlineStr">
         <is>
-          <t xml:space="preserve">5586340</t>
+          <t xml:space="preserve">384189, 384190</t>
         </is>
       </c>
       <c r="I552" t="inlineStr">
         <is>
-          <t xml:space="preserve">14</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J552">
-        <v>357</v>
+        <v>137</v>
       </c>
       <c r="K552" t="inlineStr">
         <is>
-          <t xml:space="preserve">311661783</t>
+          <t xml:space="preserve">311683914</t>
         </is>
       </c>
       <c r="L552" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tæthedskompagniet ApS</t>
+          <t xml:space="preserve">Sweco Danmark A/S - LBF</t>
         </is>
       </c>
       <c r="M552" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-02-22</t>
+          <t xml:space="preserve">2033-05-30</t>
         </is>
       </c>
       <c r="N552" t="inlineStr">
@@ -41441,30 +41441,30 @@
       </c>
       <c r="F553" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stadionvej 18</t>
+          <t xml:space="preserve">Banegårdspladsen 4</t>
         </is>
       </c>
       <c r="G553" t="inlineStr">
         <is>
-          <t xml:space="preserve">7850</t>
+          <t xml:space="preserve">8800</t>
         </is>
       </c>
       <c r="H553" t="inlineStr">
         <is>
-          <t xml:space="preserve">384189, 384190</t>
+          <t xml:space="preserve">381021, 381022, 381023, 381024, 381025</t>
         </is>
       </c>
       <c r="I553" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J553">
-        <v>137</v>
+        <v>1814</v>
       </c>
       <c r="K553" t="inlineStr">
         <is>
-          <t xml:space="preserve">311683914</t>
+          <t xml:space="preserve">311702960</t>
         </is>
       </c>
       <c r="L553" t="inlineStr">
@@ -41474,7 +41474,7 @@
       </c>
       <c r="M553" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-05-30</t>
+          <t xml:space="preserve">2033-08-27</t>
         </is>
       </c>
       <c r="N553" t="inlineStr">
@@ -41516,40 +41516,40 @@
       </c>
       <c r="F554" t="inlineStr">
         <is>
-          <t xml:space="preserve">Banegårdspladsen 4</t>
+          <t xml:space="preserve">Jørgens Alle 42</t>
         </is>
       </c>
       <c r="G554" t="inlineStr">
         <is>
-          <t xml:space="preserve">8800</t>
+          <t xml:space="preserve">8850</t>
         </is>
       </c>
       <c r="H554" t="inlineStr">
         <is>
-          <t xml:space="preserve">381021, 381022, 381023, 381024, 381025</t>
+          <t xml:space="preserve">7775696</t>
         </is>
       </c>
       <c r="I554" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="J554">
-        <v>1814</v>
+        <v>394</v>
       </c>
       <c r="K554" t="inlineStr">
         <is>
-          <t xml:space="preserve">311702960</t>
+          <t xml:space="preserve">311764588</t>
         </is>
       </c>
       <c r="L554" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sweco Danmark A/S - LBF</t>
+          <t xml:space="preserve">Ydes Bygningsrådgivning</t>
         </is>
       </c>
       <c r="M554" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-08-27</t>
+          <t xml:space="preserve">2034-06-06</t>
         </is>
       </c>
       <c r="N554" t="inlineStr">
@@ -41591,40 +41591,40 @@
       </c>
       <c r="F555" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jørgens Alle 42</t>
+          <t xml:space="preserve">Gl. Randersvej 35</t>
         </is>
       </c>
       <c r="G555" t="inlineStr">
         <is>
-          <t xml:space="preserve">8850</t>
+          <t xml:space="preserve">8800</t>
         </is>
       </c>
       <c r="H555" t="inlineStr">
         <is>
-          <t xml:space="preserve">7775696</t>
+          <t xml:space="preserve">8837678</t>
         </is>
       </c>
       <c r="I555" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J555">
-        <v>394</v>
+        <v>13000</v>
       </c>
       <c r="K555" t="inlineStr">
         <is>
-          <t xml:space="preserve">311764588</t>
+          <t xml:space="preserve">311797218</t>
         </is>
       </c>
       <c r="L555" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ydes Bygningsrådgivning</t>
+          <t xml:space="preserve">Trykprøvning &amp; Energimærkning Danmark ApS</t>
         </is>
       </c>
       <c r="M555" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-06-06</t>
+          <t xml:space="preserve">2034-11-13</t>
         </is>
       </c>
       <c r="N555" t="inlineStr">
@@ -41666,7 +41666,7 @@
       </c>
       <c r="F556" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gl. Randersvej 35</t>
+          <t xml:space="preserve">Rughavevej 66</t>
         </is>
       </c>
       <c r="G556" t="inlineStr">
@@ -41676,30 +41676,30 @@
       </c>
       <c r="H556" t="inlineStr">
         <is>
-          <t xml:space="preserve">8837678</t>
+          <t xml:space="preserve">5590174</t>
         </is>
       </c>
       <c r="I556" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">18</t>
         </is>
       </c>
       <c r="J556">
-        <v>13000</v>
+        <v>683</v>
       </c>
       <c r="K556" t="inlineStr">
         <is>
-          <t xml:space="preserve">311797218</t>
+          <t xml:space="preserve">311805525</t>
         </is>
       </c>
       <c r="L556" t="inlineStr">
         <is>
-          <t xml:space="preserve">Trykprøvning &amp; Energimærkning Danmark ApS</t>
+          <t xml:space="preserve">Tæthedskompagniet ApS</t>
         </is>
       </c>
       <c r="M556" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-11-13</t>
+          <t xml:space="preserve">2035-01-13</t>
         </is>
       </c>
       <c r="N556" t="inlineStr">
@@ -41741,7 +41741,7 @@
       </c>
       <c r="F557" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rughavevej 66</t>
+          <t xml:space="preserve">Sct. Leonis Gade 8</t>
         </is>
       </c>
       <c r="G557" t="inlineStr">
@@ -41751,30 +41751,30 @@
       </c>
       <c r="H557" t="inlineStr">
         <is>
-          <t xml:space="preserve">5590174</t>
+          <t xml:space="preserve">5585392</t>
         </is>
       </c>
       <c r="I557" t="inlineStr">
         <is>
-          <t xml:space="preserve">18</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J557">
-        <v>683</v>
+        <v>310</v>
       </c>
       <c r="K557" t="inlineStr">
         <is>
-          <t xml:space="preserve">311805525</t>
+          <t xml:space="preserve">311858724</t>
         </is>
       </c>
       <c r="L557" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tæthedskompagniet ApS</t>
+          <t xml:space="preserve">Norconsult Danmark A/S</t>
         </is>
       </c>
       <c r="M557" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-01-13</t>
+          <t xml:space="preserve">2035-09-29</t>
         </is>
       </c>
       <c r="N557" t="inlineStr">
@@ -41816,17 +41816,17 @@
       </c>
       <c r="F558" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sct. Leonis Gade 8</t>
+          <t xml:space="preserve">Iglsøvej 68B</t>
         </is>
       </c>
       <c r="G558" t="inlineStr">
         <is>
-          <t xml:space="preserve">8800</t>
+          <t xml:space="preserve">7850</t>
         </is>
       </c>
       <c r="H558" t="inlineStr">
         <is>
-          <t xml:space="preserve">5585392</t>
+          <t xml:space="preserve">4048544</t>
         </is>
       </c>
       <c r="I558" t="inlineStr">
@@ -41835,21 +41835,21 @@
         </is>
       </c>
       <c r="J558">
-        <v>310</v>
+        <v>515</v>
       </c>
       <c r="K558" t="inlineStr">
         <is>
-          <t xml:space="preserve">311858724</t>
+          <t xml:space="preserve">311869171</t>
         </is>
       </c>
       <c r="L558" t="inlineStr">
         <is>
-          <t xml:space="preserve">Norconsult Danmark A/S</t>
+          <t xml:space="preserve">Tæthedskompagniet ApS</t>
         </is>
       </c>
       <c r="M558" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-09-29</t>
+          <t xml:space="preserve">2035-11-19</t>
         </is>
       </c>
       <c r="N558" t="inlineStr">
@@ -41891,40 +41891,40 @@
       </c>
       <c r="F559" t="inlineStr">
         <is>
-          <t xml:space="preserve">Iglsøvej 68B</t>
+          <t xml:space="preserve">Martinesminde 2</t>
         </is>
       </c>
       <c r="G559" t="inlineStr">
         <is>
-          <t xml:space="preserve">7850</t>
+          <t xml:space="preserve">8800</t>
         </is>
       </c>
       <c r="H559" t="inlineStr">
         <is>
-          <t xml:space="preserve">4048544</t>
+          <t xml:space="preserve">100617942</t>
         </is>
       </c>
       <c r="I559" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J559">
-        <v>515</v>
+        <v>349</v>
       </c>
       <c r="K559" t="inlineStr">
         <is>
-          <t xml:space="preserve">311869171</t>
+          <t xml:space="preserve">311881722</t>
         </is>
       </c>
       <c r="L559" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tæthedskompagniet ApS</t>
+          <t xml:space="preserve">Sweco Danmark A/S</t>
         </is>
       </c>
       <c r="M559" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-11-19</t>
+          <t xml:space="preserve">2036-02-12</t>
         </is>
       </c>
       <c r="N559" t="inlineStr">
@@ -41966,7 +41966,7 @@
       </c>
       <c r="F560" t="inlineStr">
         <is>
-          <t xml:space="preserve">Martinesminde 2</t>
+          <t xml:space="preserve">Stænderpladsen 2</t>
         </is>
       </c>
       <c r="G560" t="inlineStr">
@@ -41976,30 +41976,30 @@
       </c>
       <c r="H560" t="inlineStr">
         <is>
-          <t xml:space="preserve">100617942</t>
+          <t xml:space="preserve">9431029</t>
         </is>
       </c>
       <c r="I560" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J560">
-        <v>349</v>
+        <v>1500</v>
       </c>
       <c r="K560" t="inlineStr">
         <is>
-          <t xml:space="preserve">311881722</t>
+          <t xml:space="preserve">311929568</t>
         </is>
       </c>
       <c r="L560" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sweco Danmark A/S</t>
+          <t xml:space="preserve">NRGi Rådgivning A/S</t>
         </is>
       </c>
       <c r="M560" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-02-12</t>
+          <t xml:space="preserve">2036-10-02</t>
         </is>
       </c>
       <c r="N560" t="inlineStr">
